--- a/technology_surveys/019_electric_vehicle_readiness_survey--technology_surveys.xlsx
+++ b/technology_surveys/019_electric_vehicle_readiness_survey--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1182,8 +1182,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'maybe'}</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Maybe'}</t>
+          <t>Maybe</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'workplace_charging'}</t>
+          <t>workplace_charging</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Workplace charging'}</t>
+          <t>Workplace charging</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'home_charging'}</t>
+          <t>home_charging</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Home charging'}</t>
+          <t>Home charging</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'public_charging'}</t>
+          <t>public_charging</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Public charging'}</t>
+          <t>Public charging</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'home'}</t>
+          <t>home</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Home'}</t>
+          <t>Home</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'workplace'}</t>
+          <t>workplace</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Workplace'}</t>
+          <t>Workplace</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'public'}</t>
+          <t>public</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Public'}</t>
+          <t>Public</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'education_and_awareness'}</t>
+          <t>education_and_awareness</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Education and awareness'}</t>
+          <t>Education and awareness</t>
         </is>
       </c>
     </row>
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'test_drive_opportunities'}</t>
+          <t>test_drive_opportunities</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Test drive opportunities'}</t>
+          <t>Test drive opportunities</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'workplace_charging_infrastructure'}</t>
+          <t>workplace_charging_infrastructure</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Workplace charging infrastructure'}</t>
+          <t>Workplace charging infrastructure</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1517,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'vehicle_pricing_and_incentives'}</t>
+          <t>vehicle_pricing_and_incentives</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Vehicle pricing and incentives'}</t>
+          <t>Vehicle pricing and incentives</t>
         </is>
       </c>
     </row>
@@ -1534,12 +1534,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1568,12 +1568,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'maybe'}</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Maybe'}</t>
+          <t>Maybe</t>
         </is>
       </c>
     </row>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'sedan'}</t>
+          <t>sedan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Sedan'}</t>
+          <t>Sedan</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'suv'}</t>
+          <t>suv</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'SUV'}</t>
+          <t>SUV</t>
         </is>
       </c>
     </row>
@@ -1636,12 +1636,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'truck'}</t>
+          <t>truck</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Truck'}</t>
+          <t>Truck</t>
         </is>
       </c>
     </row>
@@ -1653,12 +1653,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'van'}</t>
+          <t>van</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Van'}</t>
+          <t>Van</t>
         </is>
       </c>
     </row>
@@ -1670,12 +1670,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'motorcycle'}</t>
+          <t>motorcycle</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Motorcycle'}</t>
+          <t>Motorcycle</t>
         </is>
       </c>
     </row>
@@ -1687,12 +1687,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'compact'}</t>
+          <t>compact</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Compact'}</t>
+          <t>Compact</t>
         </is>
       </c>
     </row>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'full-size'}</t>
+          <t>full-size</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Full-size'}</t>
+          <t>Full-size</t>
         </is>
       </c>
     </row>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Large'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -1738,12 +1738,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'extra_large'}</t>
+          <t>extra_large</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Extra Large'}</t>
+          <t>Extra Large</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1772,12 +1772,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'black'}</t>
+          <t>black</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Black'}</t>
+          <t>Black</t>
         </is>
       </c>
     </row>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'white'}</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'White'}</t>
+          <t>White</t>
         </is>
       </c>
     </row>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'gray'}</t>
+          <t>gray</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Gray'}</t>
+          <t>Gray</t>
         </is>
       </c>
     </row>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'silver'}</t>
+          <t>silver</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Silver'}</t>
+          <t>Silver</t>
         </is>
       </c>
     </row>
@@ -1840,12 +1840,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1857,12 +1857,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'hatchback'}</t>
+          <t>hatchback</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Hatchback'}</t>
+          <t>Hatchback</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'suv'}</t>
+          <t>suv</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'SUV'}</t>
+          <t>SUV</t>
         </is>
       </c>
     </row>
@@ -1891,12 +1891,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'wagon'}</t>
+          <t>wagon</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Wagon'}</t>
+          <t>Wagon</t>
         </is>
       </c>
     </row>
@@ -1908,12 +1908,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'van'}</t>
+          <t>van</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Van'}</t>
+          <t>Van</t>
         </is>
       </c>
     </row>
@@ -1925,12 +1925,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
